--- a/Schedule/2026 Master Schedule.xlsx
+++ b/Schedule/2026 Master Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bsleeter/Documents/Documents - Benjamin's MacBook Pro/GH Baseball/Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F88146A-CEAB-2945-B7C3-AD7209D93F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38F81F7-A40D-424C-A7B0-2F8E4EDF12FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="3040" windowWidth="27300" windowHeight="14500" activeTab="1" xr2:uid="{DEE07C68-23DA-2F4F-8E1C-1A71F8558C8E}"/>
+    <workbookView xWindow="160" yWindow="1140" windowWidth="27300" windowHeight="16500" activeTab="1" xr2:uid="{DEE07C68-23DA-2F4F-8E1C-1A71F8558C8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="234">
   <si>
     <t>Date</t>
   </si>
@@ -468,9 +468,6 @@
     <t>Sehmel #1</t>
   </si>
   <si>
-    <t>8:00 - 3:00 pm</t>
-  </si>
-  <si>
     <t>Time</t>
   </si>
   <si>
@@ -600,9 +597,6 @@
     <t>GHHS</t>
   </si>
   <si>
-    <t xml:space="preserve">5:00 - 9:00 pm </t>
-  </si>
-  <si>
     <t>Sehmel #2</t>
   </si>
   <si>
@@ -684,9 +678,6 @@
     <t>11am</t>
   </si>
   <si>
-    <t xml:space="preserve">Game vs North Kitsap </t>
-  </si>
-  <si>
     <t>Game at PHS</t>
   </si>
   <si>
@@ -727,6 +718,27 @@
   </si>
   <si>
     <t xml:space="preserve">2:30-6:30 pm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game @ North Kitsap </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7:00 - 9:00 pm </t>
+  </si>
+  <si>
+    <t>6:30 - 9:00pm</t>
+  </si>
+  <si>
+    <t>6:300 - 9:00 pm</t>
+  </si>
+  <si>
+    <t>North Kitsap HS</t>
+  </si>
+  <si>
+    <t>11:00am</t>
+  </si>
+  <si>
+    <t>8:00am - 3:00 pm</t>
   </si>
 </sst>
 </file>
@@ -2430,7 +2442,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.5" customWidth="1"/>
@@ -2439,7 +2451,7 @@
     <col min="9" max="10" width="15.33203125" customWidth="1"/>
     <col min="11" max="11" width="26.33203125" customWidth="1"/>
     <col min="12" max="12" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.1640625" customWidth="1"/>
     <col min="14" max="14" width="28.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2450,12 +2462,12 @@
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
       <c r="E1" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
       <c r="H1" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
@@ -2465,28 +2477,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>1</v>
@@ -2509,7 +2521,7 @@
         <v>51</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>8</v>
@@ -2518,7 +2530,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>8</v>
@@ -2527,7 +2539,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>8</v>
@@ -2551,7 +2563,7 @@
         <v>52</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>6</v>
@@ -2560,7 +2572,7 @@
         <v>142</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>6</v>
@@ -2569,7 +2581,7 @@
         <v>142</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>6</v>
@@ -2593,7 +2605,7 @@
         <v>53</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>8</v>
@@ -2602,7 +2614,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
@@ -2611,7 +2623,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>8</v>
@@ -2635,7 +2647,7 @@
         <v>54</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>6</v>
@@ -2644,7 +2656,7 @@
         <v>142</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>8</v>
@@ -2653,7 +2665,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>8</v>
@@ -2677,7 +2689,7 @@
         <v>55</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>8</v>
@@ -2686,22 +2698,22 @@
         <v>5</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
@@ -2719,10 +2731,10 @@
         <v>56</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>143</v>
+        <v>233</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>142</v>
@@ -2763,7 +2775,7 @@
         <v>58</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>6</v>
@@ -2772,22 +2784,22 @@
         <v>142</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>11</v>
@@ -2797,7 +2809,7 @@
         <v>14</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -2805,31 +2817,31 @@
         <v>59</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2" t="s">
@@ -2847,28 +2859,28 @@
         <v>60</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>5</v>
@@ -2889,28 +2901,28 @@
         <v>61</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>5</v>
@@ -2931,7 +2943,7 @@
         <v>62</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>6</v>
@@ -2940,22 +2952,22 @@
         <v>142</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>7</v>
+        <v>146</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>11</v>
@@ -2965,7 +2977,7 @@
         <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -2973,30 +2985,32 @@
         <v>63</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="J15" s="11"/>
+        <v>232</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>231</v>
+      </c>
       <c r="K15" s="2" t="s">
         <v>18</v>
       </c>
@@ -3029,31 +3043,31 @@
         <v>65</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2" t="s">
@@ -3071,31 +3085,31 @@
         <v>66</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2" t="s">
@@ -3113,31 +3127,31 @@
         <v>67</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>7</v>
+        <v>229</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>186</v>
+        <v>5</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2" t="s">
@@ -3155,7 +3169,7 @@
         <v>68</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>6</v>
@@ -3164,22 +3178,22 @@
         <v>142</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>11</v>
@@ -3197,26 +3211,32 @@
         <v>69</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
+        <v>185</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="K21" s="2" t="s">
         <v>26</v>
       </c>
@@ -3241,13 +3261,13 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -3279,7 +3299,7 @@
         <v>72</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>6</v>
@@ -3288,22 +3308,22 @@
         <v>142</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>11</v>
@@ -3321,31 +3341,31 @@
         <v>73</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2" t="s">
@@ -3363,28 +3383,28 @@
         <v>74</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>5</v>
@@ -3405,31 +3425,31 @@
         <v>75</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I27" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2" t="s">
@@ -3447,7 +3467,7 @@
         <v>76</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>6</v>
@@ -3456,22 +3476,22 @@
         <v>142</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>11</v>
@@ -3489,10 +3509,10 @@
         <v>77</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>142</v>
@@ -3501,13 +3521,13 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
       <c r="H29" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>34</v>
@@ -3539,31 +3559,31 @@
         <v>79</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2" t="s">
@@ -3581,31 +3601,31 @@
         <v>80</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>35</v>
@@ -3615,7 +3635,7 @@
         <v>22</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -3623,28 +3643,28 @@
         <v>81</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>166</v>
-      </c>
       <c r="E33" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>5</v>
@@ -3665,31 +3685,31 @@
         <v>82</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>11</v>
@@ -3707,31 +3727,31 @@
         <v>83</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>5</v>
+        <v>186</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>163</v>
+        <v>7</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>5</v>
+        <v>185</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -3753,13 +3773,13 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
       <c r="H36" s="13" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -3789,22 +3809,22 @@
         <v>86</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>171</v>
-      </c>
       <c r="F38" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="11"/>
@@ -3825,31 +3845,31 @@
         <v>87</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>39</v>
@@ -3867,31 +3887,31 @@
         <v>88</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>11</v>
@@ -3909,31 +3929,31 @@
         <v>89</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I41" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2" t="s">
@@ -3951,31 +3971,31 @@
         <v>90</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>7</v>
+        <v>229</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>186</v>
+        <v>5</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>11</v>
@@ -3993,22 +4013,22 @@
         <v>91</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>173</v>
-      </c>
       <c r="E43" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H43" s="13"/>
       <c r="I43" s="11"/>
@@ -4043,32 +4063,26 @@
         <v>93</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>176</v>
-      </c>
       <c r="E45" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>5</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2" t="s">
         <v>6</v>
@@ -4085,31 +4099,31 @@
         <v>94</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>163</v>
+        <v>7</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>5</v>
+        <v>185</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>43</v>
@@ -4127,31 +4141,31 @@
         <v>95</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>7</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2" t="s">
@@ -4169,31 +4183,31 @@
         <v>96</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G48" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>11</v>
@@ -4211,31 +4225,31 @@
         <v>97</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>186</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I49" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2" t="s">
@@ -4259,13 +4273,13 @@
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
       <c r="H50" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
@@ -4295,31 +4309,31 @@
         <v>100</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>11</v>
@@ -4337,32 +4351,26 @@
         <v>101</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>5</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
       <c r="K53" s="2" t="s">
         <v>44</v>
       </c>
@@ -4379,31 +4387,31 @@
         <v>102</v>
       </c>
       <c r="B54" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="E54" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2" t="s">
@@ -4421,31 +4429,31 @@
         <v>103</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I55" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2" t="s">
@@ -4463,31 +4471,31 @@
         <v>104</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>11</v>
@@ -4508,22 +4516,22 @@
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>46</v>
@@ -4555,31 +4563,31 @@
         <v>107</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I59" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2" t="s">
@@ -4597,31 +4605,31 @@
         <v>108</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>47</v>
@@ -4639,32 +4647,26 @@
         <v>109</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H61" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="I61" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>5</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
       <c r="K61" s="2" t="s">
         <v>49</v>
       </c>
@@ -4681,31 +4683,31 @@
         <v>110</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>11</v>
@@ -4723,31 +4725,31 @@
         <v>111</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I63" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2" t="s">
@@ -4771,13 +4773,13 @@
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
       <c r="H64" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
@@ -4807,31 +4809,31 @@
         <v>114</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>147</v>
+        <v>182</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>199</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>5</v>
+        <v>182</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>11</v>
@@ -4848,32 +4850,20 @@
       <c r="A67" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>183</v>
-      </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
       <c r="H67" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I67" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2" t="s">
@@ -4891,31 +4881,31 @@
         <v>116</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G68" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>11</v>
@@ -4933,31 +4923,31 @@
         <v>117</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I69" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="2" t="s">
@@ -4975,38 +4965,38 @@
         <v>118</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G70" s="8" t="s">
         <v>5</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>25</v>
@@ -5053,10 +5043,10 @@
         <v>121</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>5</v>
@@ -5083,10 +5073,10 @@
         <v>122</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>142</v>
@@ -5113,10 +5103,10 @@
         <v>123</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>5</v>
@@ -5143,10 +5133,10 @@
         <v>124</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>142</v>
@@ -5173,10 +5163,10 @@
         <v>125</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>5</v>

--- a/Schedule/2026 Master Schedule.xlsx
+++ b/Schedule/2026 Master Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bsleeter/Documents/Documents - Benjamin's MacBook Pro/GH Baseball/Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38F81F7-A40D-424C-A7B0-2F8E4EDF12FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2416402E-9D59-3044-8065-8BE5B11F26C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="1140" windowWidth="27300" windowHeight="16500" activeTab="1" xr2:uid="{DEE07C68-23DA-2F4F-8E1C-1A71F8558C8E}"/>
   </bookViews>
@@ -669,9 +669,6 @@
     <t>Game vs Seillacoom (DH)</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Game vs PHS </t>
   </si>
   <si>
@@ -739,6 +736,9 @@
   </si>
   <si>
     <t>8:00am - 3:00 pm</t>
+  </si>
+  <si>
+    <t>12pm, 2pm</t>
   </si>
 </sst>
 </file>
@@ -2734,7 +2734,7 @@
         <v>147</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>142</v>
@@ -2787,7 +2787,7 @@
         <v>146</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>5</v>
@@ -2809,7 +2809,7 @@
         <v>14</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -2862,7 +2862,7 @@
         <v>148</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>151</v>
@@ -2904,7 +2904,7 @@
         <v>149</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>151</v>
@@ -2977,7 +2977,7 @@
         <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -2988,7 +2988,7 @@
         <v>150</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>142</v>
@@ -2997,7 +2997,7 @@
         <v>150</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>185</v>
@@ -3006,10 +3006,10 @@
         <v>201</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>18</v>
@@ -3088,7 +3088,7 @@
         <v>154</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>156</v>
@@ -3097,7 +3097,7 @@
         <v>189</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>156</v>
@@ -3148,7 +3148,7 @@
         <v>146</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>5</v>
@@ -3232,7 +3232,7 @@
         <v>146</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>5</v>
@@ -3311,7 +3311,7 @@
         <v>146</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>5</v>
@@ -3353,7 +3353,7 @@
         <v>191</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>160</v>
@@ -3404,7 +3404,7 @@
         <v>146</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>5</v>
@@ -3512,7 +3512,7 @@
         <v>161</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>142</v>
@@ -3524,7 +3524,7 @@
         <v>209</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>185</v>
@@ -3571,7 +3571,7 @@
         <v>146</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>186</v>
@@ -3619,7 +3619,7 @@
         <v>165</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>202</v>
@@ -3646,7 +3646,7 @@
         <v>164</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>165</v>
@@ -3739,7 +3739,7 @@
         <v>146</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>186</v>
@@ -3773,13 +3773,13 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
       <c r="H36" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>200</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -3812,7 +3812,7 @@
         <v>168</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>169</v>
@@ -3857,19 +3857,19 @@
         <v>193</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>169</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I39" s="11" t="s">
         <v>202</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>39</v>
@@ -3899,7 +3899,7 @@
         <v>146</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>5</v>
@@ -3941,7 +3941,7 @@
         <v>146</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>186</v>
@@ -3983,7 +3983,7 @@
         <v>146</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>5</v>
@@ -4016,7 +4016,7 @@
         <v>171</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>172</v>
@@ -4025,10 +4025,10 @@
         <v>194</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H43" s="13"/>
       <c r="I43" s="11"/>
@@ -4066,7 +4066,7 @@
         <v>174</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>175</v>
@@ -4075,7 +4075,7 @@
         <v>195</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>185</v>
@@ -4399,7 +4399,7 @@
         <v>198</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>178</v>
@@ -4441,7 +4441,7 @@
         <v>146</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>186</v>
@@ -4483,7 +4483,7 @@
         <v>146</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>5</v>
@@ -4519,7 +4519,7 @@
         <v>161</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>185</v>
@@ -4528,10 +4528,10 @@
         <v>161</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>46</v>
@@ -4575,7 +4575,7 @@
         <v>146</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>186</v>
@@ -4623,13 +4623,13 @@
         <v>185</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>202</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>47</v>
@@ -4695,7 +4695,7 @@
         <v>146</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>5</v>
@@ -4737,7 +4737,7 @@
         <v>146</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>186</v>
@@ -4812,7 +4812,7 @@
         <v>181</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>182</v>
@@ -4821,7 +4821,7 @@
         <v>199</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>182</v>
@@ -4935,7 +4935,7 @@
         <v>146</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G69" s="8" t="s">
         <v>186</v>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>25</v>
